--- a/artfynd/A 34485-2025 artfynd.xlsx
+++ b/artfynd/A 34485-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>126313824</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34485-2025 artfynd.xlsx
+++ b/artfynd/A 34485-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>126313824</v>
       </c>
       <c r="B10" t="n">
-        <v>91596</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34485-2025 artfynd.xlsx
+++ b/artfynd/A 34485-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>126313824</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34485-2025 artfynd.xlsx
+++ b/artfynd/A 34485-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>126313824</v>
       </c>
       <c r="B10" t="n">
-        <v>91603</v>
+        <v>91596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34485-2025 artfynd.xlsx
+++ b/artfynd/A 34485-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>126313824</v>
       </c>
       <c r="B10" t="n">
-        <v>91596</v>
+        <v>91603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
